--- a/filer/25652991_puregym.xlsx
+++ b/filer/25652991_puregym.xlsx
@@ -7578,7 +7578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7654,21 +7654,27 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndAmortisationOfIntangibleAssets</t>
+          <t>fsa:AmountOfIncomeCostItemsWhichAreSpecialDueToSizeAndNature</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndAmortisationOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>413368</v>
-      </c>
-      <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n"/>
-      <c r="H3" s="35" t="n"/>
+          <t>fsa:AmountOfIncomeCostItemsWhichAreSpecialDueToSizeAndNature</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n">
+        <v>120500</v>
+      </c>
+      <c r="F3" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="35" t="n">
+        <v>-16766</v>
+      </c>
+      <c r="H3" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7683,21 +7689,27 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
+          <t>fsa:InterestExpenseToParticipatingInterests</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n">
-        <v>856756</v>
-      </c>
-      <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
-      <c r="H4" s="38" t="n"/>
+          <t>fsa:InterestExpenseToParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n"/>
+      <c r="E4" s="38" t="n">
+        <v>3657</v>
+      </c>
+      <c r="F4" s="38" t="n">
+        <v>3820</v>
+      </c>
+      <c r="G4" s="38" t="n">
+        <v>5405</v>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>7384</v>
+      </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7712,21 +7724,21 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssets</t>
+          <t>fsa:LongtermTradePayables</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>85217</v>
-      </c>
+          <t>fsa:LongtermTradePayables</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
+      <c r="H5" s="35" t="n">
+        <v>16946</v>
+      </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7741,429 +7753,26 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipment</t>
+          <t>fsa:RefundInJointAssessment</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>115327</v>
-      </c>
+          <t>fsa:RefundInJointAssessment</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="38" t="n"/>
+      <c r="F6" s="38" t="n">
+        <v>-508</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>163</v>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>fsa:AmountOfIncomeCostItemsWhichAreSpecialDueToSizeAndNature</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>fsa:AmountOfIncomeCostItemsWhichAreSpecialDueToSizeAndNature</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
-        <v>120500</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="35" t="n">
-        <v>-16766</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n"/>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="38" t="n"/>
-      <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>67527</v>
-      </c>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>100280</v>
-      </c>
-      <c r="E10" s="38" t="n">
-        <v>8385</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>1016</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>174</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n">
-        <v>4846</v>
-      </c>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n">
-        <v>37445</v>
-      </c>
-      <c r="G11" s="35" t="n">
-        <v>23714</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>40717</v>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughTransfers</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughTransfers</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n"/>
-      <c r="H12" s="38" t="n"/>
-      <c r="I12" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IntangibleAssetsGross</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IntangibleAssetsGross</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>559088</v>
-      </c>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>fsa:InterestExpenseToParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>fsa:InterestExpenseToParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n">
-        <v>3657</v>
-      </c>
-      <c r="F14" s="38" t="n">
-        <v>3820</v>
-      </c>
-      <c r="G14" s="38" t="n">
-        <v>5405</v>
-      </c>
-      <c r="H14" s="38" t="n">
-        <v>7384</v>
-      </c>
-      <c r="I14" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>fsa:LongtermTradePayables</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>fsa:LongtermTradePayables</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n">
-        <v>16946</v>
-      </c>
-      <c r="I15" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>fsa:PropertyPlantAndEquipmentGross</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>fsa:PropertyPlantAndEquipmentGross</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n">
-        <v>1245834</v>
-      </c>
-      <c r="E16" s="38" t="n"/>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="38" t="n"/>
-      <c r="I16" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>fsa:RefundInJointAssessment</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>fsa:RefundInJointAssessment</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n">
-        <v>-508</v>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>163</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>58282</v>
-      </c>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/25652991_puregym.xlsx
+++ b/filer/25652991_puregym.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/25652991_puregym.xlsx
+++ b/filer/25652991_puregym.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +677,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1531,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -3009,35 +3009,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4343,19 +4343,19 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -4461,19 +4461,19 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
@@ -4771,6 +4771,13 @@
       <c r="F98" s="13">
         <f>IFERROR($F$36/($F$61+$F$67)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4802,19 +4809,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4824,19 +4831,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>914953</v>
+        <v>768149</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>768149</v>
+        <v>1189258</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1189258</v>
+        <v>1195178</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>1195178</v>
+        <v>1187681</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1187681</v>
+        <v>1176484</v>
       </c>
     </row>
     <row r="3">
@@ -4846,19 +4853,19 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>184186</v>
+        <v>206076</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>206076</v>
+        <v>485</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>485</v>
+        <v>997</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>997</v>
+        <v>13484</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>13484</v>
+        <v>11267</v>
       </c>
     </row>
     <row r="4">
@@ -4868,19 +4875,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>75647</v>
+        <v>50576</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>50576</v>
+        <v>77900</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>77900</v>
+        <v>80912</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>80912</v>
+        <v>70230</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>70230</v>
+        <v>50957</v>
       </c>
     </row>
     <row r="5">
@@ -4890,19 +4897,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>706838</v>
+        <v>630891</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>630891</v>
+        <v>677139</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>677139</v>
+        <v>693318</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>693318</v>
+        <v>655035</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>655035</v>
+        <v>592522</v>
       </c>
     </row>
     <row r="6">
@@ -4912,19 +4919,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>316654</v>
+        <v>292758</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>292758</v>
+        <v>434704</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>434704</v>
+        <v>421945</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>421945</v>
+        <v>475900</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>475900</v>
+        <v>544272</v>
       </c>
     </row>
     <row r="7">
@@ -4934,19 +4941,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>388570</v>
+        <v>394008</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>394008</v>
+        <v>318034</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>318034</v>
+        <v>313685</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>313685</v>
+        <v>285536</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>285536</v>
+        <v>273862</v>
       </c>
     </row>
     <row r="8">
@@ -4963,19 +4970,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>271012</v>
+        <v>158360</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>158360</v>
+        <v>177726</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>177726</v>
+        <v>145299</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>145299</v>
+        <v>156670</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>156670</v>
+        <v>99474</v>
       </c>
     </row>
     <row r="10">
@@ -4984,18 +4991,20 @@
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
+      <c r="B10" s="16" t="n">
+        <v>11035</v>
+      </c>
       <c r="C10" s="16" t="n">
-        <v>11035</v>
+        <v>6158</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>6158</v>
+        <v>10389</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>10389</v>
+        <v>5550</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>5550</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="11">
@@ -5005,19 +5014,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>-342928</v>
+        <v>-270645</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-270645</v>
+        <v>-67214</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>-67214</v>
+        <v>-47428</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-47428</v>
+        <v>28144</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>28144</v>
+        <v>168760</v>
       </c>
     </row>
     <row r="12">
@@ -5027,11 +5036,9 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>-33194</v>
-      </c>
-      <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="C12" s="16" t="n"/>
       <c r="D12" s="16" t="n"/>
       <c r="E12" s="16" t="n"/>
       <c r="F12" s="16" t="n"/>
@@ -5043,19 +5050,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>159</v>
+        <v>1501</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>1501</v>
+        <v>5103</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>5103</v>
+        <v>2472</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>2472</v>
+        <v>3132</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>3132</v>
+        <v>999</v>
       </c>
     </row>
     <row r="14">
@@ -5065,19 +5072,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>9051</v>
+        <v>9571</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>9571</v>
+        <v>9819</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>9819</v>
+        <v>9055</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>9055</v>
+        <v>17594</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>17594</v>
+        <v>13840</v>
       </c>
     </row>
     <row r="15">
@@ -5087,19 +5094,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>-8892</v>
+        <v>-8070</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>-8070</v>
+        <v>-4716</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>-4716</v>
+        <v>-6583</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-6583</v>
+        <v>-14462</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>-14462</v>
+        <v>-12841</v>
       </c>
     </row>
     <row r="16">
@@ -5109,19 +5116,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>-385014</v>
+        <v>-278715</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>-278715</v>
+        <v>-71930</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>-71930</v>
+        <v>-54011</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-54011</v>
+        <v>13682</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>13682</v>
+        <v>155919</v>
       </c>
     </row>
     <row r="17">
@@ -5131,19 +5138,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>-55478</v>
+        <v>-57262</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>-57262</v>
+        <v>-48866</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>-48866</v>
+        <v>-4649</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-4649</v>
+        <v>4690</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>4690</v>
+        <v>35465</v>
       </c>
     </row>
     <row r="18">
@@ -5153,19 +5160,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>-329536</v>
+        <v>-221453</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>-221453</v>
+        <v>-23064</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>-23064</v>
+        <v>-49362</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-49362</v>
+        <v>8992</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>8992</v>
+        <v>120454</v>
       </c>
     </row>
     <row r="19">
@@ -5175,19 +5182,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>1</v>
+        <v>1036</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>1036</v>
+        <v>678</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>597</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20">
@@ -5197,19 +5204,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>47800</v>
+        <v>17014</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>17014</v>
+        <v>158086</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>158086</v>
+        <v>105166</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>105166</v>
+        <v>311010</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>311010</v>
+        <v>146394</v>
       </c>
     </row>
   </sheetData>
@@ -5241,19 +5248,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -5263,19 +5270,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>30256</v>
+        <v>4315</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>4315</v>
+        <v>2556</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2556</v>
+        <v>4583</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>4583</v>
+        <v>1742</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1742</v>
+        <v>17876</v>
       </c>
     </row>
     <row r="3">
@@ -5285,16 +5292,16 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>480</v>
+        <v>18654</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>18654</v>
+        <v>8775</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>8775</v>
+        <v>1215</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>1215</v>
+        <v>0</v>
       </c>
       <c r="F3" s="16" t="n">
         <v>0</v>
@@ -5307,19 +5314,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>84692</v>
+        <v>59734</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>59734</v>
+        <v>39641</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>39641</v>
+        <v>23151</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>23151</v>
+        <v>7297</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>7297</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="5">
@@ -5329,19 +5336,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>145720</v>
+        <v>83063</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>83063</v>
+        <v>51212</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>51212</v>
+        <v>29069</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>29069</v>
+        <v>22825</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>22825</v>
+        <v>24605</v>
       </c>
     </row>
     <row r="6">
@@ -5375,19 +5382,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>216896</v>
+        <v>161850</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>161850</v>
+        <v>119267</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>119267</v>
+        <v>112490</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>112490</v>
+        <v>250770</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>250770</v>
+        <v>280449</v>
       </c>
     </row>
     <row r="9">
@@ -5397,19 +5404,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>144420</v>
+        <v>133150</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>133150</v>
+        <v>170396</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>170396</v>
+        <v>149834</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>149834</v>
+        <v>179935</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>179935</v>
+        <v>192795</v>
       </c>
     </row>
     <row r="10">
@@ -5419,19 +5426,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>27762</v>
+        <v>2884</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>2884</v>
+        <v>7592</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>7592</v>
+        <v>8336</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>8336</v>
+        <v>3604</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>3604</v>
+        <v>9985</v>
       </c>
     </row>
     <row r="11">
@@ -5441,19 +5448,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>389078</v>
+        <v>297884</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>297884</v>
+        <v>297255</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>297255</v>
+        <v>270660</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>270660</v>
+        <v>434309</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>434309</v>
+        <v>483229</v>
       </c>
     </row>
     <row r="12">
@@ -5485,19 +5492,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>48476</v>
+        <v>52140</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>52140</v>
+        <v>48692</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>48692</v>
+        <v>51771</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>51771</v>
+        <v>51728</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>51728</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="14">
@@ -5507,19 +5514,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>48476</v>
+        <v>52140</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>52140</v>
+        <v>48692</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>48692</v>
+        <v>51771</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>51771</v>
+        <v>51728</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>51728</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="15">
@@ -5529,19 +5536,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>583274</v>
+        <v>433087</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>433087</v>
+        <v>397159</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>397159</v>
+        <v>351500</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>351500</v>
+        <v>508862</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>508862</v>
+        <v>554090</v>
       </c>
     </row>
     <row r="16">
@@ -5574,18 +5581,20 @@
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="16" t="n">
+        <v>10734</v>
+      </c>
       <c r="C18" s="16" t="n">
-        <v>10734</v>
+        <v>15332</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>15332</v>
+        <v>9392</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>9392</v>
+        <v>9023</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>9023</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="19">
@@ -5595,19 +5604,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>12123</v>
+        <v>10734</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>10734</v>
+        <v>15332</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>15332</v>
+        <v>9392</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>9392</v>
+        <v>9023</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>9023</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="20">
@@ -5617,19 +5626,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>12452</v>
+        <v>21590</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>21590</v>
+        <v>19296</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>19296</v>
+        <v>11127</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>11127</v>
+        <v>8465</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>8465</v>
+        <v>15747</v>
       </c>
     </row>
     <row r="21">
@@ -5639,19 +5648,19 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>15145</v>
+        <v>9392</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>9392</v>
+        <v>8678</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>8678</v>
+        <v>17499</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>17499</v>
+        <v>1812</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>1812</v>
+        <v>708</v>
       </c>
     </row>
     <row r="22">
@@ -5661,19 +5670,19 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>28465</v>
+        <v>4231</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>4231</v>
+        <v>4876</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>4876</v>
+        <v>6106</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>6106</v>
+        <v>4320</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>4320</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="23">
@@ -5683,19 +5692,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>8763</v>
+        <v>9056</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>9056</v>
+        <v>11315</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>11315</v>
+        <v>19506</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>19506</v>
+        <v>23352</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>23352</v>
+        <v>23467</v>
       </c>
     </row>
     <row r="24">
@@ -5705,19 +5714,19 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>26558</v>
+        <v>76371</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>76371</v>
+        <v>122460</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>122460</v>
+        <v>129869</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>129869</v>
+        <v>124991</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>124991</v>
+        <v>90877</v>
       </c>
     </row>
     <row r="25">
@@ -5726,16 +5735,16 @@
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
+      <c r="B25" s="16" t="n">
+        <v>751</v>
+      </c>
       <c r="C25" s="16" t="n">
-        <v>751</v>
+        <v>508</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>508</v>
-      </c>
-      <c r="E25" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="E25" s="16" t="n"/>
       <c r="F25" s="16" t="n"/>
     </row>
     <row r="26">
@@ -5757,19 +5766,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>91383</v>
+        <v>121391</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>121391</v>
+        <v>167133</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>167133</v>
+        <v>184107</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>184107</v>
+        <v>162940</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>162940</v>
+        <v>134648</v>
       </c>
     </row>
     <row r="28">
@@ -5791,19 +5800,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>11577</v>
+        <v>95597</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>95597</v>
+        <v>13668</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>13668</v>
+        <v>94904</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>94904</v>
+        <v>74359</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>74359</v>
+        <v>81994</v>
       </c>
     </row>
     <row r="30">
@@ -5813,19 +5822,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>115083</v>
+        <v>227722</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>227722</v>
+        <v>196133</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>196133</v>
+        <v>288403</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>288403</v>
+        <v>246322</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>246322</v>
+        <v>223049</v>
       </c>
     </row>
     <row r="31">
@@ -5835,19 +5844,19 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>698357</v>
+        <v>660809</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>660809</v>
+        <v>593292</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>593292</v>
+        <v>639903</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>639903</v>
+        <v>755184</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>755184</v>
+        <v>777139</v>
       </c>
     </row>
     <row r="32">
@@ -5891,19 +5900,19 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>18751</v>
+        <v>3749</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>3749</v>
+        <v>773</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>0</v>
+        <v>10382</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>10382</v>
+        <v>14659</v>
       </c>
     </row>
     <row r="35">
@@ -5937,19 +5946,19 @@
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>57</v>
+        <v>-206393</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>-206393</v>
+        <v>23519</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>23519</v>
+        <v>74930</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>74930</v>
+        <v>49695</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>49695</v>
+        <v>165872</v>
       </c>
     </row>
     <row r="38">
@@ -5959,19 +5968,19 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>19699</v>
+        <v>-201753</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>-201753</v>
+        <v>25183</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>25183</v>
+        <v>75821</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>75821</v>
+        <v>60968</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>60968</v>
+        <v>181422</v>
       </c>
     </row>
     <row r="39">
@@ -5981,19 +5990,19 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>82851</v>
+        <v>60073</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>60073</v>
+        <v>103961</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>103961</v>
+        <v>131334</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>131334</v>
+        <v>124804</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>124804</v>
+        <v>87296</v>
       </c>
     </row>
     <row r="40">
@@ -6027,19 +6036,19 @@
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>70578</v>
+        <v>35994</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>35994</v>
+        <v>17227</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>17227</v>
+        <v>6270</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>6270</v>
+        <v>916</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6049,19 +6058,19 @@
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>27153</v>
+        <v>44983</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>44983</v>
+        <v>19942</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>19942</v>
+        <v>144813</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>144813</v>
+        <v>151278</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>151278</v>
+        <v>203938</v>
       </c>
     </row>
     <row r="44">
@@ -6071,19 +6080,19 @@
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>179662</v>
+        <v>166565</v>
       </c>
       <c r="C44" s="16" t="n">
-        <v>166565</v>
+        <v>126578</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>126578</v>
+        <v>169387</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>169387</v>
+        <v>187443</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>187443</v>
+        <v>236909</v>
       </c>
     </row>
     <row r="45">
@@ -6104,18 +6113,20 @@
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
+      <c r="B46" s="16" t="n">
+        <v>35447</v>
+      </c>
       <c r="C46" s="16" t="n">
-        <v>35447</v>
+        <v>18769</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>18769</v>
+        <v>10957</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>10957</v>
+        <v>8131</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>8131</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="47">
@@ -6124,9 +6135,7 @@
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B47" s="16" t="n"/>
       <c r="C47" s="16" t="n"/>
       <c r="D47" s="16" t="n"/>
       <c r="E47" s="16" t="n"/>
@@ -6138,9 +6147,7 @@
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v>36658</v>
-      </c>
+      <c r="B48" s="16" t="n"/>
       <c r="C48" s="16" t="n"/>
       <c r="D48" s="16" t="n"/>
       <c r="E48" s="16" t="n"/>
@@ -6153,19 +6160,19 @@
         </is>
       </c>
       <c r="B49" s="16" t="n">
-        <v>108306</v>
+        <v>81355</v>
       </c>
       <c r="C49" s="16" t="n">
-        <v>81355</v>
+        <v>80173</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>80173</v>
+        <v>84865</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>84865</v>
+        <v>209725</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>209725</v>
+        <v>118325</v>
       </c>
     </row>
     <row r="50">
@@ -6175,19 +6182,19 @@
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>59543</v>
+        <v>379266</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>379266</v>
+        <v>208768</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>208768</v>
+        <v>116050</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>116050</v>
+        <v>110127</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>110127</v>
+        <v>95992</v>
       </c>
     </row>
     <row r="51">
@@ -6221,17 +6228,17 @@
         </is>
       </c>
       <c r="B53" s="16" t="n">
-        <v>7850</v>
-      </c>
-      <c r="C53" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="16" t="n"/>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n">
+        <v>163</v>
+      </c>
       <c r="E53" s="16" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="54">
@@ -6241,19 +6248,19 @@
         </is>
       </c>
       <c r="B54" s="16" t="n">
-        <v>60919</v>
+        <v>67816</v>
       </c>
       <c r="C54" s="16" t="n">
-        <v>67816</v>
+        <v>17252</v>
       </c>
       <c r="D54" s="16" t="n">
-        <v>17252</v>
+        <v>40026</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>40026</v>
+        <v>44128</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>44128</v>
+        <v>32745</v>
       </c>
     </row>
     <row r="55">
@@ -6263,19 +6270,19 @@
         </is>
       </c>
       <c r="B55" s="16" t="n">
-        <v>142869</v>
+        <v>72040</v>
       </c>
       <c r="C55" s="16" t="n">
-        <v>72040</v>
+        <v>12608</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>12608</v>
+        <v>11300</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>11300</v>
+        <v>9858</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>9858</v>
+        <v>20150</v>
       </c>
     </row>
     <row r="56">
@@ -6285,19 +6292,19 @@
         </is>
       </c>
       <c r="B56" s="16" t="n">
-        <v>416145</v>
+        <v>635924</v>
       </c>
       <c r="C56" s="16" t="n">
-        <v>635924</v>
+        <v>337570</v>
       </c>
       <c r="D56" s="16" t="n">
-        <v>337570</v>
+        <v>263361</v>
       </c>
       <c r="E56" s="16" t="n">
-        <v>263361</v>
+        <v>381969</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>381969</v>
+        <v>271512</v>
       </c>
     </row>
     <row r="57">
@@ -6307,19 +6314,19 @@
         </is>
       </c>
       <c r="B57" s="16" t="n">
-        <v>595807</v>
+        <v>802489</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>802489</v>
+        <v>464148</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>464148</v>
+        <v>432748</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>432748</v>
+        <v>569412</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>569412</v>
+        <v>508421</v>
       </c>
     </row>
     <row r="58">
@@ -6329,19 +6336,19 @@
         </is>
       </c>
       <c r="B58" s="16" t="n">
-        <v>698357</v>
+        <v>660809</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>660809</v>
+        <v>593292</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>593292</v>
+        <v>639903</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>639903</v>
+        <v>755184</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>755184</v>
+        <v>777139</v>
       </c>
     </row>
   </sheetData>
@@ -6380,13 +6387,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7100,7 +7107,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7218,7 +7225,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7394,7 +7401,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7617,27 +7624,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7662,18 +7669,20 @@
           <t>fsa:AmountOfIncomeCostItemsWhichAreSpecialDueToSizeAndNature</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n"/>
+      <c r="D3" s="35" t="n">
+        <v>120500</v>
+      </c>
       <c r="E3" s="35" t="n">
-        <v>120500</v>
+        <v>0</v>
       </c>
       <c r="F3" s="35" t="n">
+        <v>-16766</v>
+      </c>
+      <c r="G3" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="35" t="n">
-        <v>-16766</v>
-      </c>
       <c r="H3" s="35" t="n">
-        <v>0</v>
+        <v>-24175</v>
       </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7697,18 +7706,20 @@
           <t>fsa:InterestExpenseToParticipatingInterests</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n"/>
+      <c r="D4" s="38" t="n">
+        <v>3657</v>
+      </c>
       <c r="E4" s="38" t="n">
-        <v>3657</v>
+        <v>3820</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>3820</v>
+        <v>5405</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>5405</v>
+        <v>7384</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>7384</v>
+        <v>8261</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7735,9 +7746,11 @@
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
+      <c r="G5" s="35" t="n">
+        <v>16946</v>
+      </c>
       <c r="H5" s="35" t="n">
-        <v>16946</v>
+        <v>13997</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7762,15 +7775,17 @@
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
+      <c r="E6" s="38" t="n">
+        <v>-508</v>
+      </c>
       <c r="F6" s="38" t="n">
-        <v>-508</v>
+        <v>163</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
